--- a/experiment/test/results-B100/B100.xlsx
+++ b/experiment/test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.12</v>
+        <v>25.02</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5779</v>
+        <v>0.6599</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.76</v>
+        <v>30.13</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8152</v>
+        <v>0.8628</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.71</v>
+        <v>27.82</v>
       </c>
       <c r="C4" t="n">
-        <v>0.819</v>
+        <v>0.8568</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.68</v>
+        <v>32.33</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8505</v>
+        <v>0.9028</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.28</v>
+        <v>27.49</v>
       </c>
       <c r="C6" t="n">
-        <v>0.713</v>
+        <v>0.79</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.09</v>
+        <v>35.38</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8948</v>
+        <v>0.9196</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.47</v>
+        <v>28.51</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7578</v>
+        <v>0.8459</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.12</v>
+        <v>24.44</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5952</v>
+        <v>0.7114</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.53</v>
+        <v>28.91</v>
       </c>
       <c r="C10" t="n">
-        <v>0.79</v>
+        <v>0.8495</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29.36</v>
+        <v>30.91</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8052</v>
+        <v>0.8617</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.91</v>
+        <v>26.47</v>
       </c>
       <c r="C12" t="n">
-        <v>0.752</v>
+        <v>0.8228</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.18</v>
+        <v>30.35</v>
       </c>
       <c r="C13" t="n">
-        <v>0.762</v>
+        <v>0.8474</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.07</v>
+        <v>31.82</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8097</v>
+        <v>0.8778</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.61</v>
+        <v>30.99</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8371</v>
+        <v>0.8771</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.11</v>
+        <v>26.44</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6819</v>
+        <v>0.7698</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.95</v>
+        <v>27.46</v>
       </c>
       <c r="C17" t="n">
-        <v>0.7673</v>
+        <v>0.8539</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.9</v>
+        <v>36.12</v>
       </c>
       <c r="C18" t="n">
-        <v>0.896</v>
+        <v>0.9204</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33.09</v>
+        <v>34.51</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8962</v>
+        <v>0.9233</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26.33</v>
+        <v>27.31</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7418</v>
+        <v>0.7913</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26.09</v>
+        <v>27.43</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8041</v>
+        <v>0.8478</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.25</v>
+        <v>23.9</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6977</v>
+        <v>0.7919</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24.1</v>
+        <v>25.6</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6442</v>
+        <v>0.7455000000000001</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24.86</v>
+        <v>25.74</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5744</v>
+        <v>0.6566</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.71</v>
+        <v>28.21</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7989000000000001</v>
+        <v>0.8628</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27.78</v>
+        <v>29.7</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8252</v>
+        <v>0.8838</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.02</v>
+        <v>28.8</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8409</v>
+        <v>0.8885</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.89</v>
+        <v>29.33</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7413999999999999</v>
+        <v>0.8090000000000001</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.66</v>
+        <v>31.41</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8055</v>
+        <v>0.8653999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.8</v>
+        <v>34.35</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9035</v>
+        <v>0.93</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.92</v>
+        <v>20.91</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5102</v>
+        <v>0.6108</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.89</v>
+        <v>31.84</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8197</v>
+        <v>0.8861</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.97</v>
+        <v>22.02</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4375</v>
+        <v>0.5683</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.26</v>
+        <v>26.88</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6772</v>
+        <v>0.7785</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.54</v>
+        <v>25.66</v>
       </c>
       <c r="C35" t="n">
-        <v>0.7624</v>
+        <v>0.8198</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>35.21</v>
+        <v>36.73</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8958</v>
+        <v>0.9205</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27.1</v>
+        <v>28.62</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7453</v>
+        <v>0.8115</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.96</v>
+        <v>28.56</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5139</v>
+        <v>0.5806</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.36</v>
+        <v>29.28</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7211</v>
+        <v>0.7727000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.54</v>
+        <v>30.33</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7494</v>
+        <v>0.8377</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36.86</v>
+        <v>39.08</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9619</v>
+        <v>0.9747</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>27.05</v>
+        <v>28.59</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7522</v>
+        <v>0.8072</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.99</v>
+        <v>27.11</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7295</v>
+        <v>0.7866</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.87</v>
+        <v>28.35</v>
       </c>
       <c r="C44" t="n">
-        <v>0.765</v>
+        <v>0.8159</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.2</v>
+        <v>30.06</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8803</v>
+        <v>0.9209000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.89</v>
+        <v>26.14</v>
       </c>
       <c r="C46" t="n">
-        <v>0.695</v>
+        <v>0.7705</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.82</v>
+        <v>35.88</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8741</v>
+        <v>0.9016999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.88</v>
+        <v>24.46</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6324</v>
+        <v>0.73</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25.01</v>
+        <v>26.36</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6372</v>
+        <v>0.7422</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.66</v>
+        <v>30</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8834</v>
+        <v>0.9285</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.2</v>
+        <v>33.43</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8411999999999999</v>
+        <v>0.8748</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.93</v>
+        <v>26.04</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6248</v>
+        <v>0.7084</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.82</v>
+        <v>24.6</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7136</v>
+        <v>0.7894</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.66</v>
+        <v>33.47</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8483000000000001</v>
+        <v>0.8761</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.59</v>
+        <v>33.67</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8016</v>
+        <v>0.8442</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.95</v>
+        <v>29.81</v>
       </c>
       <c r="C56" t="n">
-        <v>0.7853</v>
+        <v>0.852</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.7</v>
+        <v>27.36</v>
       </c>
       <c r="C57" t="n">
-        <v>0.6992</v>
+        <v>0.7864</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>21.49</v>
+        <v>22.33</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4297</v>
+        <v>0.5423</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27.52</v>
+        <v>28.63</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7302</v>
+        <v>0.7917999999999999</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32.02</v>
+        <v>32.97</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7925</v>
+        <v>0.8341</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.34</v>
+        <v>32.1</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7873</v>
+        <v>0.8237</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.81</v>
+        <v>32.76</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8171</v>
+        <v>0.8512999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>29.09</v>
+        <v>30.41</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7952</v>
+        <v>0.8448</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>34.32</v>
+        <v>37</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9543</v>
+        <v>0.9675</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.37</v>
+        <v>25.84</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6751</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>26.11</v>
+        <v>27.31</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6237</v>
+        <v>0.7101</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.4</v>
+        <v>29.97</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7961</v>
+        <v>0.8536</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>40.41</v>
+        <v>42.54</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9817</v>
+        <v>0.9858</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.1</v>
+        <v>22.56</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5884</v>
+        <v>0.7016</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22.81</v>
+        <v>23.86</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6552</v>
+        <v>0.7335</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>29.12</v>
+        <v>30.96</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8162</v>
+        <v>0.8666</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.83</v>
+        <v>32.4</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8268</v>
+        <v>0.8621</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25.49</v>
+        <v>26.91</v>
       </c>
       <c r="C73" t="n">
-        <v>0.599</v>
+        <v>0.7083</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>27.22</v>
+        <v>28.31</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6069</v>
+        <v>0.6968</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.34</v>
+        <v>27.41</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6978</v>
+        <v>0.7634</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>24.22</v>
+        <v>25.71</v>
       </c>
       <c r="C76" t="n">
-        <v>0.705</v>
+        <v>0.7723</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.71</v>
+        <v>31.84</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7857</v>
+        <v>0.8374</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23.65</v>
+        <v>24.64</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4808</v>
+        <v>0.5993000000000001</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>29.83</v>
+        <v>31.51</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8123</v>
+        <v>0.8682</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>33.14</v>
+        <v>35.08</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9552</v>
+        <v>0.9664</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.79</v>
+        <v>30.87</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8199</v>
+        <v>0.8648</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.99</v>
+        <v>37.6</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9403</v>
+        <v>0.9536</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.61</v>
+        <v>29.36</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7229</v>
+        <v>0.7674</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.3</v>
+        <v>23.4</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5365</v>
+        <v>0.645</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>21.11</v>
+        <v>22.22</v>
       </c>
       <c r="C85" t="n">
-        <v>0.6141</v>
+        <v>0.7023</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25.8</v>
+        <v>26.97</v>
       </c>
       <c r="C86" t="n">
-        <v>0.796</v>
+        <v>0.8487</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25.08</v>
+        <v>26.37</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6078</v>
+        <v>0.712</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.44</v>
+        <v>28.52</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6993</v>
+        <v>0.7753</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30.84</v>
+        <v>32.54</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8166</v>
+        <v>0.8745000000000001</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>27.25</v>
+        <v>28.13</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5612</v>
+        <v>0.6457000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.22</v>
+        <v>26.88</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6546999999999999</v>
+        <v>0.7685</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>29.18</v>
+        <v>30.63</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7177</v>
+        <v>0.7946</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>26.94</v>
+        <v>28.52</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7659</v>
+        <v>0.8244</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>31.07</v>
+        <v>33.51</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8814</v>
+        <v>0.9288999999999999</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26.14</v>
+        <v>27.76</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7237</v>
+        <v>0.8094</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.61</v>
+        <v>28.81</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8183</v>
+        <v>0.8816000000000001</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>21.93</v>
+        <v>22.46</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3201</v>
+        <v>0.4205</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>27.06</v>
+        <v>27.93</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5634</v>
+        <v>0.6455</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26.36</v>
+        <v>27.76</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7819</v>
+        <v>0.8461</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>27.02</v>
+        <v>28.42</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7402</v>
+        <v>0.8082</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.23</v>
+        <v>26.73</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7369</v>
+        <v>0.8096</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.69</v>
+        <v>29.11</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7409</v>
+        <v>0.8061</v>
       </c>
     </row>
   </sheetData>

--- a/experiment/test/results-B100/B100.xlsx
+++ b/experiment/test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25.02</v>
+        <v>23.39</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6599</v>
+        <v>0.5312</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30.13</v>
+        <v>27.61</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8628</v>
+        <v>0.783</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>27.82</v>
+        <v>25.46</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8568</v>
+        <v>0.771</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>32.33</v>
+        <v>29.67</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9028</v>
+        <v>0.8235</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.49</v>
+        <v>25.8</v>
       </c>
       <c r="C6" t="n">
-        <v>0.79</v>
+        <v>0.6879999999999999</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>35.38</v>
+        <v>31.88</v>
       </c>
       <c r="C7" t="n">
-        <v>0.9196</v>
+        <v>0.8745000000000001</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>28.51</v>
+        <v>25.28</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8459</v>
+        <v>0.7027</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24.44</v>
+        <v>22.75</v>
       </c>
       <c r="C9" t="n">
-        <v>0.7114</v>
+        <v>0.5647</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28.91</v>
+        <v>26.65</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8495</v>
+        <v>0.758</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30.91</v>
+        <v>28.66</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8617</v>
+        <v>0.7812</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>26.47</v>
+        <v>22.56</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8228</v>
+        <v>0.6213</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30.35</v>
+        <v>26.78</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8474</v>
+        <v>0.6918</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31.82</v>
+        <v>29.52</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8778</v>
+        <v>0.7919</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>30.99</v>
+        <v>27.82</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8771</v>
+        <v>0.7865</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26.44</v>
+        <v>24.49</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7698</v>
+        <v>0.6478</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27.46</v>
+        <v>23.18</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8539</v>
+        <v>0.6739000000000001</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>36.12</v>
+        <v>32.94</v>
       </c>
       <c r="C18" t="n">
-        <v>0.9204</v>
+        <v>0.8641</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34.51</v>
+        <v>31.91</v>
       </c>
       <c r="C19" t="n">
-        <v>0.9233</v>
+        <v>0.8713</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>27.31</v>
+        <v>24.59</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7913</v>
+        <v>0.6803</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>27.43</v>
+        <v>24.99</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8478</v>
+        <v>0.7637</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>23.9</v>
+        <v>21.15</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7919</v>
+        <v>0.5948</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>25.6</v>
+        <v>22.92</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7455000000000001</v>
+        <v>0.5651</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>25.74</v>
+        <v>24.61</v>
       </c>
       <c r="C24" t="n">
-        <v>0.6566</v>
+        <v>0.553</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28.21</v>
+        <v>25.47</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8628</v>
+        <v>0.7347</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29.7</v>
+        <v>26.31</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8838</v>
+        <v>0.7712</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28.8</v>
+        <v>26.16</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8885</v>
+        <v>0.8076</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29.33</v>
+        <v>26.93</v>
       </c>
       <c r="C28" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.703</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.41</v>
+        <v>28.98</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8653999999999999</v>
+        <v>0.7788</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>34.35</v>
+        <v>28.88</v>
       </c>
       <c r="C30" t="n">
-        <v>0.93</v>
+        <v>0.8563</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>20.91</v>
+        <v>19.57</v>
       </c>
       <c r="C31" t="n">
-        <v>0.6108</v>
+        <v>0.4701</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>31.84</v>
+        <v>29.11</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8861</v>
+        <v>0.7977</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>22.02</v>
+        <v>20.72</v>
       </c>
       <c r="C33" t="n">
-        <v>0.5683</v>
+        <v>0.3957</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26.88</v>
+        <v>24.57</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7785</v>
+        <v>0.6301</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>25.66</v>
+        <v>23.61</v>
       </c>
       <c r="C35" t="n">
-        <v>0.8198</v>
+        <v>0.708</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>36.73</v>
+        <v>31.61</v>
       </c>
       <c r="C36" t="n">
-        <v>0.9205</v>
+        <v>0.855</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28.62</v>
+        <v>25.95</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8115</v>
+        <v>0.6955</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>28.56</v>
+        <v>27.65</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5806</v>
+        <v>0.5076000000000001</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29.28</v>
+        <v>27.21</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7727000000000001</v>
+        <v>0.6839</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30.33</v>
+        <v>27.56</v>
       </c>
       <c r="C40" t="n">
-        <v>0.8377</v>
+        <v>0.7043</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>39.08</v>
+        <v>30.09</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9747</v>
+        <v>0.87</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>28.59</v>
+        <v>25.42</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8072</v>
+        <v>0.6911</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>27.11</v>
+        <v>24.72</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7866</v>
+        <v>0.6657999999999999</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>28.35</v>
+        <v>25.62</v>
       </c>
       <c r="C44" t="n">
-        <v>0.8159</v>
+        <v>0.7201</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>30.06</v>
+        <v>26.04</v>
       </c>
       <c r="C45" t="n">
-        <v>0.9209000000000001</v>
+        <v>0.8217</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>26.14</v>
+        <v>24.18</v>
       </c>
       <c r="C46" t="n">
-        <v>0.7705</v>
+        <v>0.6353</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>35.88</v>
+        <v>33.1</v>
       </c>
       <c r="C47" t="n">
-        <v>0.9016999999999999</v>
+        <v>0.8428</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>24.46</v>
+        <v>21.94</v>
       </c>
       <c r="C48" t="n">
-        <v>0.73</v>
+        <v>0.5644</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>26.36</v>
+        <v>24.58</v>
       </c>
       <c r="C49" t="n">
-        <v>0.7422</v>
+        <v>0.6085</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>30</v>
+        <v>24.4</v>
       </c>
       <c r="C50" t="n">
-        <v>0.9285</v>
+        <v>0.7887999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>33.43</v>
+        <v>31.28</v>
       </c>
       <c r="C51" t="n">
-        <v>0.8748</v>
+        <v>0.8197</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>26.04</v>
+        <v>24.41</v>
       </c>
       <c r="C52" t="n">
-        <v>0.7084</v>
+        <v>0.5893</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>24.6</v>
+        <v>21.65</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7894</v>
+        <v>0.667</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>33.47</v>
+        <v>31.4</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8761</v>
+        <v>0.8225</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>33.67</v>
+        <v>32.23</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8442</v>
+        <v>0.7884</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29.81</v>
+        <v>26.21</v>
       </c>
       <c r="C56" t="n">
-        <v>0.852</v>
+        <v>0.7079</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>27.36</v>
+        <v>24.25</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7864</v>
+        <v>0.6297</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>22.33</v>
+        <v>21.18</v>
       </c>
       <c r="C58" t="n">
-        <v>0.5423</v>
+        <v>0.3961</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>28.63</v>
+        <v>26.94</v>
       </c>
       <c r="C59" t="n">
-        <v>0.7917999999999999</v>
+        <v>0.6968</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>32.97</v>
+        <v>31.79</v>
       </c>
       <c r="C60" t="n">
-        <v>0.8341</v>
+        <v>0.7849</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>32.1</v>
+        <v>29.79</v>
       </c>
       <c r="C61" t="n">
-        <v>0.8237</v>
+        <v>0.7491</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>32.76</v>
+        <v>31.13</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8512999999999999</v>
+        <v>0.7936</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>30.41</v>
+        <v>27.75</v>
       </c>
       <c r="C63" t="n">
-        <v>0.8448</v>
+        <v>0.7639</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>37</v>
+        <v>28.98</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9675</v>
+        <v>0.9107</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>25.84</v>
+        <v>23.9</v>
       </c>
       <c r="C65" t="n">
-        <v>0.779</v>
+        <v>0.646</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>27.31</v>
+        <v>25.18</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7101</v>
+        <v>0.5879</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>29.97</v>
+        <v>27.25</v>
       </c>
       <c r="C67" t="n">
-        <v>0.8536</v>
+        <v>0.7609</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>42.54</v>
+        <v>35.53</v>
       </c>
       <c r="C68" t="n">
-        <v>0.9858</v>
+        <v>0.9618</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>22.56</v>
+        <v>20.45</v>
       </c>
       <c r="C69" t="n">
-        <v>0.7016</v>
+        <v>0.532</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>23.86</v>
+        <v>22.28</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7335</v>
+        <v>0.6187</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>30.96</v>
+        <v>26.92</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8666</v>
+        <v>0.7621</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>32.4</v>
+        <v>28.35</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8621</v>
+        <v>0.752</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>26.91</v>
+        <v>24.97</v>
       </c>
       <c r="C73" t="n">
-        <v>0.7083</v>
+        <v>0.5705</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>28.31</v>
+        <v>27.03</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6968</v>
+        <v>0.5941</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>27.41</v>
+        <v>25.71</v>
       </c>
       <c r="C75" t="n">
-        <v>0.7634</v>
+        <v>0.6706</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>25.71</v>
+        <v>22.84</v>
       </c>
       <c r="C76" t="n">
-        <v>0.7723</v>
+        <v>0.6296</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>31.84</v>
+        <v>29.79</v>
       </c>
       <c r="C77" t="n">
-        <v>0.8374</v>
+        <v>0.7635999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>24.64</v>
+        <v>23.48</v>
       </c>
       <c r="C78" t="n">
-        <v>0.5993000000000001</v>
+        <v>0.461</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>31.51</v>
+        <v>28.95</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8682</v>
+        <v>0.7864</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>35.08</v>
+        <v>27.67</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9664</v>
+        <v>0.8826000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>30.87</v>
+        <v>29.54</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8648</v>
+        <v>0.8096</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>37.6</v>
+        <v>34.09</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9536</v>
+        <v>0.9214</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>29.36</v>
+        <v>27.97</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7674</v>
+        <v>0.6933</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>23.4</v>
+        <v>21.78</v>
       </c>
       <c r="C84" t="n">
-        <v>0.645</v>
+        <v>0.4887</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>22.22</v>
+        <v>20.72</v>
       </c>
       <c r="C85" t="n">
-        <v>0.7023</v>
+        <v>0.5574</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>26.97</v>
+        <v>24</v>
       </c>
       <c r="C86" t="n">
-        <v>0.8487</v>
+        <v>0.7125</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>26.37</v>
+        <v>24.35</v>
       </c>
       <c r="C87" t="n">
-        <v>0.712</v>
+        <v>0.5614</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>28.52</v>
+        <v>26.81</v>
       </c>
       <c r="C88" t="n">
-        <v>0.7753</v>
+        <v>0.6608000000000001</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>32.54</v>
+        <v>29.47</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8745000000000001</v>
+        <v>0.7758</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>28.13</v>
+        <v>26.92</v>
       </c>
       <c r="C90" t="n">
-        <v>0.6457000000000001</v>
+        <v>0.5456</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>26.88</v>
+        <v>24.72</v>
       </c>
       <c r="C91" t="n">
-        <v>0.7685</v>
+        <v>0.6126</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>30.63</v>
+        <v>28.45</v>
       </c>
       <c r="C92" t="n">
-        <v>0.7946</v>
+        <v>0.6909</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>28.52</v>
+        <v>24.83</v>
       </c>
       <c r="C93" t="n">
-        <v>0.8244</v>
+        <v>0.6696</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>33.51</v>
+        <v>29.34</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.8614000000000001</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>27.76</v>
+        <v>24.61</v>
       </c>
       <c r="C95" t="n">
-        <v>0.8094</v>
+        <v>0.6482</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>28.81</v>
+        <v>24.56</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8816000000000001</v>
+        <v>0.7265</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>22.46</v>
+        <v>21.88</v>
       </c>
       <c r="C97" t="n">
-        <v>0.4205</v>
+        <v>0.3074</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>27.93</v>
+        <v>26.81</v>
       </c>
       <c r="C98" t="n">
-        <v>0.6455</v>
+        <v>0.5475</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>27.76</v>
+        <v>25.49</v>
       </c>
       <c r="C99" t="n">
-        <v>0.8461</v>
+        <v>0.7507</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>28.42</v>
+        <v>25.69</v>
       </c>
       <c r="C100" t="n">
-        <v>0.8082</v>
+        <v>0.6725</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>26.73</v>
+        <v>23.83</v>
       </c>
       <c r="C101" t="n">
-        <v>0.8096</v>
+        <v>0.6589</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>29.11</v>
+        <v>26.4</v>
       </c>
       <c r="C102" t="n">
-        <v>0.8061</v>
+        <v>0.6966</v>
       </c>
     </row>
   </sheetData>

--- a/experiment/test/results-B100/B100.xlsx
+++ b/experiment/test/results-B100/B100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24.09</v>
+        <v>24.03</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5748</v>
+        <v>0.5718</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>28.78</v>
+        <v>28.73</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8147</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>26.67</v>
+        <v>26.49</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8156</v>
+        <v>0.8119</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30.66</v>
+        <v>30.58</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8498</v>
+        <v>0.8478</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>26.27</v>
+        <v>26.25</v>
       </c>
       <c r="C6" t="n">
-        <v>0.7116</v>
+        <v>0.7117</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34.05</v>
+        <v>33.87</v>
       </c>
       <c r="C7" t="n">
-        <v>0.8944</v>
+        <v>0.8933</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>26.37</v>
+        <v>26.31</v>
       </c>
       <c r="C8" t="n">
-        <v>0.7542</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.14</v>
+        <v>23.09</v>
       </c>
       <c r="C9" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.5923</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>27.54</v>
+        <v>27.4</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7895</v>
+        <v>0.7871</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
         <v>29.35</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8046</v>
+        <v>0.8048</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24.71</v>
+        <v>24.58</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7423</v>
+        <v>0.7342</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28.04</v>
+        <v>28</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7568</v>
+        <v>0.7527</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30.08</v>
+        <v>30.04</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8099</v>
+        <v>0.8092</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29.38</v>
+        <v>29.41</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8335</v>
+        <v>0.8318</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.09</v>
+        <v>25.06</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6812</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24.98</v>
+        <v>24.8</v>
       </c>
       <c r="C17" t="n">
-        <v>0.764</v>
+        <v>0.7607</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>34.85</v>
+        <v>34.79</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.8932</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>33.04</v>
+        <v>32.93</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8949</v>
+        <v>0.8934</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>26.27</v>
+        <v>26.18</v>
       </c>
       <c r="C20" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.7387</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26.14</v>
+        <v>25.97</v>
       </c>
       <c r="C21" t="n">
-        <v>0.8026</v>
+        <v>0.799</v>
       </c>
     </row>
     <row r="22">
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>22.36</v>
+        <v>22.18</v>
       </c>
       <c r="C22" t="n">
-        <v>0.6987</v>
+        <v>0.6931</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>24.04</v>
+        <v>23.93</v>
       </c>
       <c r="C23" t="n">
-        <v>0.6411</v>
+        <v>0.633</v>
       </c>
     </row>
     <row r="24">
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>24.87</v>
+        <v>24.84</v>
       </c>
       <c r="C24" t="n">
-        <v>0.5748</v>
+        <v>0.5731000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>26.66</v>
+        <v>26.61</v>
       </c>
       <c r="C25" t="n">
-        <v>0.7965</v>
+        <v>0.7961</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27.79</v>
+        <v>27.66</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8249</v>
+        <v>0.8224</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.06</v>
+        <v>27.01</v>
       </c>
       <c r="C27" t="n">
-        <v>0.8397</v>
+        <v>0.8399</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27.82</v>
+        <v>27.76</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7395</v>
+        <v>0.7387</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29.65</v>
+        <v>29.57</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8044</v>
+        <v>0.8027</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>32.72</v>
+        <v>32.45</v>
       </c>
       <c r="C30" t="n">
-        <v>0.9041</v>
+        <v>0.901</v>
       </c>
     </row>
     <row r="31">
@@ -829,10 +829,10 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>19.94</v>
+        <v>19.89</v>
       </c>
       <c r="C31" t="n">
-        <v>0.5079</v>
+        <v>0.5065</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29.87</v>
+        <v>29.79</v>
       </c>
       <c r="C32" t="n">
-        <v>0.8195</v>
+        <v>0.8178</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>20.98</v>
+        <v>20.93</v>
       </c>
       <c r="C33" t="n">
-        <v>0.4341</v>
+        <v>0.4307</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>25.25</v>
+        <v>25.18</v>
       </c>
       <c r="C34" t="n">
-        <v>0.6746</v>
+        <v>0.6727</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>24.59</v>
+        <v>24.46</v>
       </c>
       <c r="C35" t="n">
-        <v>0.762</v>
+        <v>0.7587</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>34.92</v>
+        <v>35.01</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8937</v>
+        <v>0.8935</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>27.09</v>
+        <v>27</v>
       </c>
       <c r="C37" t="n">
-        <v>0.7449</v>
+        <v>0.7423999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>27.95</v>
+        <v>27.93</v>
       </c>
       <c r="C38" t="n">
-        <v>0.5148</v>
+        <v>0.5137</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>28.34</v>
+        <v>28.27</v>
       </c>
       <c r="C39" t="n">
-        <v>0.7207</v>
+        <v>0.7171999999999999</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>28.58</v>
+        <v>28.48</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7484</v>
+        <v>0.7453</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>36.26</v>
+        <v>36.12</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9579</v>
+        <v>0.9569</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>26.95</v>
+        <v>26.85</v>
       </c>
       <c r="C42" t="n">
-        <v>0.7478</v>
+        <v>0.7455000000000001</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>25.93</v>
+        <v>25.85</v>
       </c>
       <c r="C43" t="n">
-        <v>0.7258</v>
+        <v>0.7242</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>26.78</v>
+        <v>26.77</v>
       </c>
       <c r="C44" t="n">
-        <v>0.7616000000000001</v>
+        <v>0.7607</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>28.12</v>
+        <v>27.99</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8781</v>
+        <v>0.8762</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>24.84</v>
+        <v>24.77</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6896</v>
+        <v>0.6832</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>34.82</v>
+        <v>34.67</v>
       </c>
       <c r="C47" t="n">
-        <v>0.8736</v>
+        <v>0.8714</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>22.88</v>
+        <v>22.84</v>
       </c>
       <c r="C48" t="n">
-        <v>0.6292</v>
+        <v>0.6269</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>25.02</v>
+        <v>24.99</v>
       </c>
       <c r="C49" t="n">
-        <v>0.6379</v>
+        <v>0.6359</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>27.48</v>
+        <v>27.3</v>
       </c>
       <c r="C50" t="n">
-        <v>0.8787</v>
+        <v>0.8756</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>32.2</v>
+        <v>32.18</v>
       </c>
       <c r="C51" t="n">
-        <v>0.841</v>
+        <v>0.8401999999999999</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>24.94</v>
+        <v>24.84</v>
       </c>
       <c r="C52" t="n">
-        <v>0.6245000000000001</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="53">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>22.71</v>
+        <v>22.67</v>
       </c>
       <c r="C53" t="n">
-        <v>0.7089</v>
+        <v>0.707</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>32.55</v>
+        <v>32.5</v>
       </c>
       <c r="C54" t="n">
-        <v>0.8465</v>
+        <v>0.8455</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>32.55</v>
+        <v>32.59</v>
       </c>
       <c r="C55" t="n">
-        <v>0.8002</v>
+        <v>0.8014</v>
       </c>
     </row>
     <row r="56">
@@ -1154,10 +1154,10 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>27.96</v>
+        <v>27.78</v>
       </c>
       <c r="C56" t="n">
-        <v>0.785</v>
+        <v>0.7779</v>
       </c>
     </row>
     <row r="57">
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>25.74</v>
+        <v>25.62</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7004</v>
+        <v>0.6947</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>21.5</v>
+        <v>21.43</v>
       </c>
       <c r="C58" t="n">
-        <v>0.4286</v>
+        <v>0.4241</v>
       </c>
     </row>
     <row r="59">
@@ -1193,7 +1193,7 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>27.51</v>
+        <v>27.52</v>
       </c>
       <c r="C59" t="n">
         <v>0.729</v>
@@ -1209,7 +1209,7 @@
         <v>32.01</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7927999999999999</v>
+        <v>0.7923</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31.29</v>
+        <v>31.24</v>
       </c>
       <c r="C61" t="n">
-        <v>0.7867</v>
+        <v>0.7851</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31.8</v>
+        <v>31.75</v>
       </c>
       <c r="C62" t="n">
-        <v>0.8171</v>
+        <v>0.8154</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>29.09</v>
+        <v>28.93</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7957</v>
+        <v>0.7916</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>34.09</v>
+        <v>33.75</v>
       </c>
       <c r="C64" t="n">
-        <v>0.9536</v>
+        <v>0.9523</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>24.37</v>
+        <v>24.32</v>
       </c>
       <c r="C65" t="n">
-        <v>0.6743</v>
+        <v>0.6729000000000001</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>26.09</v>
+        <v>26.05</v>
       </c>
       <c r="C66" t="n">
-        <v>0.6237</v>
+        <v>0.6213</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>28.36</v>
+        <v>28.32</v>
       </c>
       <c r="C67" t="n">
-        <v>0.7948</v>
+        <v>0.7941</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>40.12</v>
+        <v>39.87</v>
       </c>
       <c r="C68" t="n">
-        <v>0.981</v>
+        <v>0.9808</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>21.12</v>
+        <v>21.03</v>
       </c>
       <c r="C69" t="n">
-        <v>0.5846</v>
+        <v>0.5818</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>22.83</v>
+        <v>22.76</v>
       </c>
       <c r="C70" t="n">
-        <v>0.6531</v>
+        <v>0.6499</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>29.04</v>
+        <v>28.96</v>
       </c>
       <c r="C71" t="n">
-        <v>0.8149</v>
+        <v>0.8110000000000001</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>30.71</v>
+        <v>30.61</v>
       </c>
       <c r="C72" t="n">
-        <v>0.8228</v>
+        <v>0.8202</v>
       </c>
     </row>
     <row r="73">
@@ -1375,10 +1375,10 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>25.5</v>
+        <v>25.48</v>
       </c>
       <c r="C73" t="n">
-        <v>0.5988</v>
+        <v>0.5981</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>27.22</v>
+        <v>27.21</v>
       </c>
       <c r="C74" t="n">
-        <v>0.6063</v>
+        <v>0.6056</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>26.33</v>
+        <v>26.28</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6979</v>
+        <v>0.6961000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>24.18</v>
+        <v>24.14</v>
       </c>
       <c r="C76" t="n">
-        <v>0.7004</v>
+        <v>0.6986</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>30.7</v>
+        <v>30.69</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7855</v>
+        <v>0.7852</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>23.68</v>
+        <v>23.66</v>
       </c>
       <c r="C78" t="n">
-        <v>0.4795</v>
+        <v>0.48</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>29.84</v>
+        <v>29.82</v>
       </c>
       <c r="C79" t="n">
-        <v>0.8117</v>
+        <v>0.8113</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>32.99</v>
+        <v>32.62</v>
       </c>
       <c r="C80" t="n">
-        <v>0.9530999999999999</v>
+        <v>0.9516</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>29.77</v>
+        <v>29.79</v>
       </c>
       <c r="C81" t="n">
-        <v>0.8195</v>
+        <v>0.8198</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>35.94</v>
+        <v>35.85</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9398</v>
+        <v>0.9389999999999999</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>28.56</v>
+        <v>28.52</v>
       </c>
       <c r="C83" t="n">
-        <v>0.7202</v>
+        <v>0.7185</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.31</v>
+        <v>22.22</v>
       </c>
       <c r="C84" t="n">
-        <v>0.5338000000000001</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>21.11</v>
+        <v>21.03</v>
       </c>
       <c r="C85" t="n">
-        <v>0.609</v>
+        <v>0.6086</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>25.73</v>
+        <v>25.57</v>
       </c>
       <c r="C86" t="n">
-        <v>0.7923</v>
+        <v>0.7885</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>25.08</v>
+        <v>25.03</v>
       </c>
       <c r="C87" t="n">
-        <v>0.6056</v>
+        <v>0.6025</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.41</v>
+        <v>27.37</v>
       </c>
       <c r="C88" t="n">
-        <v>0.6978</v>
+        <v>0.6945</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>30.81</v>
+        <v>30.73</v>
       </c>
       <c r="C89" t="n">
-        <v>0.8159</v>
+        <v>0.8141</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>27.24</v>
+        <v>27.25</v>
       </c>
       <c r="C90" t="n">
-        <v>0.5623</v>
+        <v>0.5614</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>25.21</v>
+        <v>25.08</v>
       </c>
       <c r="C91" t="n">
-        <v>0.6535</v>
+        <v>0.6457000000000001</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>29.16</v>
+        <v>29.11</v>
       </c>
       <c r="C92" t="n">
-        <v>0.716</v>
+        <v>0.715</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>27.02</v>
+        <v>26.64</v>
       </c>
       <c r="C93" t="n">
-        <v>0.7664</v>
+        <v>0.7521</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>31.06</v>
+        <v>30.76</v>
       </c>
       <c r="C94" t="n">
-        <v>0.8808</v>
+        <v>0.8783</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26.09</v>
+        <v>25.94</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7206</v>
+        <v>0.7147</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>26.53</v>
+        <v>26.3</v>
       </c>
       <c r="C96" t="n">
-        <v>0.8141</v>
+        <v>0.8062</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>21.95</v>
+        <v>21.9</v>
       </c>
       <c r="C97" t="n">
-        <v>0.3214</v>
+        <v>0.3172</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>27.04</v>
+        <v>27.03</v>
       </c>
       <c r="C98" t="n">
-        <v>0.5635</v>
+        <v>0.5625</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>26.38</v>
+        <v>26.28</v>
       </c>
       <c r="C99" t="n">
-        <v>0.7805</v>
+        <v>0.779</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>26.97</v>
+        <v>26.91</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7371</v>
+        <v>0.7356</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.26</v>
+        <v>25.06</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7341</v>
+        <v>0.7264</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>27.65</v>
+        <v>27.56</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7393</v>
+        <v>0.7368</v>
       </c>
     </row>
   </sheetData>
